--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N197_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N197_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.00321908498329</v>
+        <v>5.363023101309784</v>
       </c>
       <c r="D2" t="n">
-        <v>28.43418353337892</v>
+        <v>4.620554824174074</v>
       </c>
       <c r="E2" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F2" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.88064783825362</v>
+        <v>2.905605273716214</v>
       </c>
       <c r="D3" t="n">
-        <v>15.80293595227422</v>
+        <v>2.567977092244561</v>
       </c>
       <c r="E3" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F3" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.04312720209755</v>
+        <v>4.557008170340853</v>
       </c>
       <c r="D4" t="n">
-        <v>28.536929751951</v>
+        <v>4.637251084692037</v>
       </c>
       <c r="E4" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F4" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.92971853898752</v>
+        <v>3.076079262585471</v>
       </c>
       <c r="D5" t="n">
-        <v>21.91298075739407</v>
+        <v>3.560859373076537</v>
       </c>
       <c r="E5" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F5" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.16330515682468</v>
+        <v>2.301537087984011</v>
       </c>
       <c r="D6" t="n">
-        <v>11.73981456944658</v>
+        <v>1.90771986753507</v>
       </c>
       <c r="E6" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F6" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.90524655984757</v>
+        <v>2.74710256597523</v>
       </c>
       <c r="D7" t="n">
-        <v>15.8902485820707</v>
+        <v>2.58216539458649</v>
       </c>
       <c r="E7" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F7" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.14887622119001</v>
+        <v>2.136692385943377</v>
       </c>
       <c r="D8" t="n">
-        <v>12.4816282091615</v>
+        <v>2.028264583988744</v>
       </c>
       <c r="E8" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F8" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.48474536030119</v>
+        <v>4.466271121048944</v>
       </c>
       <c r="D9" t="n">
-        <v>27.38907275512406</v>
+        <v>4.45072432270766</v>
       </c>
       <c r="E9" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F9" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.63013807852984</v>
+        <v>4.3273974377611</v>
       </c>
       <c r="D10" t="n">
-        <v>21.70829334609241</v>
+        <v>3.527597668740017</v>
       </c>
       <c r="E10" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F10" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.28142095117364</v>
+        <v>3.295730904565717</v>
       </c>
       <c r="D11" t="n">
-        <v>19.93434668199869</v>
+        <v>3.239331335824788</v>
       </c>
       <c r="E11" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F11" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>22.94814820664372</v>
+        <v>3.729074083579604</v>
       </c>
       <c r="D12" t="n">
-        <v>19.02054697249948</v>
+        <v>3.090838883031165</v>
       </c>
       <c r="E12" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F12" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>4.584822044952892</v>
+        <v>0.745033582304845</v>
       </c>
       <c r="D13" t="n">
-        <v>4.645778747778787</v>
+        <v>0.754939046514053</v>
       </c>
       <c r="E13" t="n">
-        <v>7.500212109406279</v>
+        <v>1.21878446777852</v>
       </c>
       <c r="F13" t="n">
-        <v>7.000838786659397</v>
+        <v>1.137636302832152</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
